--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-16.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-16.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583986162352</v>
+        <v>5583987251935</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Raelma</t>
+          <t>Mercia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raelma de Oliveira</t>
+          <t>Mercia Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583987175246</v>
+        <v>5583999743652</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lucineia</t>
+          <t>Arthur</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lucineia Carvalho da Silva</t>
+          <t>Arthur Vinicios</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583988776275</v>
+        <v>5581998510204</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hercules</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hercules Cordeiro</t>
+          <t>Andre Tavares</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583988339520</v>
+        <v>5583999196276</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jair</t>
+          <t>Weslley</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jair Evariso da Silva</t>
+          <t>Weslley Lucas</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583987791288</v>
+        <v>5583991115796</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Natanael</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Samuel do Nascimento Dantas</t>
+          <t>Natanael Pereira Duda</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583982315550</v>
+        <v>5583993013580</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Marcia</t>
+          <t>Darlyana</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Marcia Maria Nascimento dos Santos</t>
+          <t>Darlyana Costa dos Santos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583987445070</v>
+        <v>5583993937878</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Severino</t>
+          <t>Ivanildo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Severino Martinho Fernandes</t>
+          <t>Ivanildo Gomes Ramos</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583988738966</v>
+        <v>5583988985748</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amilton</t>
+          <t>Madalena</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amilton Ribeiro</t>
+          <t>Madalena da Silva Souza</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583993095562</v>
+        <v>5561984073484</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oceanica</t>
+          <t>Edificio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oceanica Cabo Branco</t>
+          <t>Edificio Residencial Glaucia Maria</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583998465626</v>
+        <v>5583996030595</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Edificio</t>
+          <t>Clesio</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Edificio Residencial Cristo Redentor Iii</t>
+          <t>Clesio Luis Leite</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583999427322</v>
+        <v>5521982299342</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dinarte</t>
+          <t>Ariberto</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dinarte Henrique da Silva</t>
+          <t>Ariberto Mendonça Falcao</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583991439133</v>
+        <v>5583986162352</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dafonte</t>
+          <t>Raelma</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dafonte</t>
+          <t>Raelma de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5565996985615</v>
+        <v>5583987175246</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Lucineia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sandra Maria Oliveira da Costa</t>
+          <t>Lucineia Carvalho da Silva</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5511981227435</v>
+        <v>5583988776275</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Hercules</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Francisco Valeriano Corcino</t>
+          <t>Hercules Cordeiro</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583991364641</v>
+        <v>5583988339520</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Georgio</t>
+          <t>Jair</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgio Ulisses da Silva Souza</t>
+          <t>Jair Evariso da Silva</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583998122375</v>
+        <v>5583987791288</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wemerson</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wemerson Rodrigues do Nascimento</t>
+          <t>Samuel do Nascimento Dantas</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583987559843</v>
+        <v>5583982315550</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kaline</t>
+          <t>Marcia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kaline Ingreed Lopes de Souza</t>
+          <t>Marcia Maria Nascimento dos Santos</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583998596161</v>
+        <v>5583987445070</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Iranildo</t>
+          <t>Severino</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iranildo Gomes da Silva</t>
+          <t>Severino Martinho Fernandes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583996075959</v>
+        <v>5583988738966</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Madalena</t>
+          <t>Amilton</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Madalena Aguiar de Lima</t>
+          <t>Amilton Ribeiro</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583986223951</v>
+        <v>5583993095562</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wendell</t>
+          <t>Oceanica</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wendell Menezes da Silva</t>
+          <t>Oceanica Cabo Branco</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583988522330</v>
+        <v>5583998465626</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Edificio</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Carlos Alberto Silva de Lima</t>
+          <t>Edificio Residencial Cristo Redentor Iii</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583986306087</v>
+        <v>5583999427322</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Dinarte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fabio Cesar de Melo Luna</t>
+          <t>Dinarte Henrique da Silva</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583986060040</v>
+        <v>5583991439133</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lucinaldo</t>
+          <t>Dafonte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lucinaldo Lins de Castro</t>
+          <t>Dafonte</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583986401497</v>
+        <v>5565996985615</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Brenndo</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brenndo dos Santos Silva</t>
+          <t>Sandra Maria Oliveira da Costa</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583986760150</v>
+        <v>5511981227435</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rosa</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rosa Maria Nascimento</t>
+          <t>Francisco Valeriano Corcino</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583988215163</v>
+        <v>5583991364641</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Georgio</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Antonio Ferreira da Silva</t>
+          <t>Georgio Ulisses da Silva Souza</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583986506145</v>
+        <v>5583998122375</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adaildon</t>
+          <t>Wemerson</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Adaildon de Oliveira Pereira</t>
+          <t>Wemerson Rodrigues do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583988984110</v>
+        <v>5583987559843</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Edificio</t>
+          <t>Kaline</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Edificio Residencial Colorado</t>
+          <t>Kaline Ingreed Lopes de Souza</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583988483691</v>
+        <v>5583998596161</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bruno</t>
+          <t>Iranildo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bruno Ferreira Souza</t>
+          <t>Iranildo Gomes da Silva</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583987140028</v>
+        <v>5583996075959</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Madalena</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>David Jhons Oliveira do Nascimento</t>
+          <t>Madalena Aguiar de Lima</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583988630623</v>
+        <v>5583986223951</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Edcleisson</t>
+          <t>Wendell</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Edcleisson Evangelista dos Santos</t>
+          <t>Wendell Menezes da Silva</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583986638522</v>
+        <v>5583988522330</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Angela Maria Lacerda Guerra</t>
+          <t>Carlos Alberto Silva de Lima</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583986256801</v>
+        <v>5583986306087</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Young Style Exclusiva</t>
+          <t>Fabio Cesar de Melo Luna</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5584991141618</v>
+        <v>5583986060040</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Lucinaldo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pedro Henrique Juvencio</t>
+          <t>Lucinaldo Lins de Castro</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583986682658</v>
+        <v>5583986401497</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jeferson</t>
+          <t>Brenndo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jeferson Almeida</t>
+          <t>Brenndo dos Santos Silva</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583996872950</v>
+        <v>5583986760150</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Rosa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ana Suely Goncalves</t>
+          <t>Rosa Maria Nascimento</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583991175282</v>
+        <v>5583988215163</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Julia Fernandes de Oliveira</t>
+          <t>Antonio Ferreira da Silva</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583981435714</v>
+        <v>5583986506145</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Adaildon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Carlos Celli Junior</t>
+          <t>Adaildon de Oliveira Pereira</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583988751041</v>
+        <v>5583988984110</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Edificio</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Leandro Ramos Mesquita</t>
+          <t>Edificio Residencial Colorado</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5595991592211</v>
+        <v>5583988483691</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wanderlene</t>
+          <t>Bruno</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wanderlene de Melo Costa</t>
+          <t>Bruno Ferreira Souza</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583986187703</v>
+        <v>5583987140028</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Djacir</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Djacir Pereira Meirelhes</t>
+          <t>David Jhons Oliveira do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583991657537</v>
+        <v>5583988630623</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gilberto</t>
+          <t>Edcleisson</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gilberto Barbosa de Lima Filho</t>
+          <t>Edcleisson Evangelista dos Santos</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583986070196</v>
+        <v>5583986638522</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gilson</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gilson Alexandre Silva</t>
+          <t>Angela Maria Lacerda Guerra</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583981479481</v>
+        <v>5583986256801</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Manuel Silvio</t>
+          <t>Young Style Exclusiva</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583999855056</v>
+        <v>5584991141618</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Djalma</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Djalma Dias Ramalho</t>
+          <t>Pedro Henrique Juvencio</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583987105020</v>
+        <v>5583986682658</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Jeferson</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fabio Jose Farias Aguiar</t>
+          <t>Jeferson Almeida</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583988564555</v>
+        <v>5583996872950</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jeova</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jeova Luiz dos Santos</t>
+          <t>Ana Suely Goncalves</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583999158598</v>
+        <v>5583991175282</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ivanildo</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ivanildo Ribeiro de Souza</t>
+          <t>Julia Fernandes de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583999124334</v>
+        <v>5583981435714</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Walmir</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Walmir Braz</t>
+          <t>Carlos Celli Junior</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583986712237</v>
+        <v>5583988751041</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ana Paula de Almeida Lima</t>
+          <t>Leandro Ramos Mesquita</t>
         </is>
       </c>
     </row>
